--- a/docs/Logic Requirements/Ageipelago Alaric.xlsx
+++ b/docs/Logic Requirements/Ageipelago Alaric.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stefb\OneDrive\Desktop\Logic Requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{063FEC41-98DE-432D-AFBC-0CC28231198C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16689149-45DA-408D-AF92-9C5334439F00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{B80992DC-780F-4856-A6B0-D26FA95FCBC0}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{B80992DC-780F-4856-A6B0-D26FA95FCBC0}"/>
   </bookViews>
   <sheets>
     <sheet name="Alaric" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="194">
   <si>
     <t>Scenario</t>
   </si>
@@ -3400,6 +3400,21 @@
       <t>:
 Murder Holes are researched automatically</t>
     </r>
+  </si>
+  <si>
+    <t>Starting Units</t>
+  </si>
+  <si>
+    <t>Starting Buildings</t>
+  </si>
+  <si>
+    <t>Item-Units</t>
+  </si>
+  <si>
+    <t>Item-Buildings</t>
+  </si>
+  <si>
+    <t>Spearman</t>
   </si>
 </sst>
 </file>
@@ -3596,7 +3611,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -3756,11 +3771,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3885,9 +3911,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3904,6 +3927,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4539,18 +4571,18 @@
   <dimension ref="B1:L42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="2" max="5" width="22.5703125" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="43" t="s">
+      <c r="B2" s="42" t="s">
         <v>175</v>
       </c>
-      <c r="C2" s="44"/>
-      <c r="D2" s="45"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="44"/>
       <c r="G2" s="2" t="s">
         <v>76</v>
       </c>
@@ -4565,11 +4597,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="46" t="s">
+      <c r="B3" s="45" t="s">
         <v>181</v>
       </c>
-      <c r="C3" s="47"/>
-      <c r="D3" s="48"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="47"/>
       <c r="G3" s="13" t="s">
         <v>78</v>
       </c>
@@ -4646,7 +4678,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="41"/>
       <c r="C7" s="41"/>
       <c r="D7" s="18"/>
@@ -4663,10 +4695,19 @@
         <v>79</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="42"/>
-      <c r="C8" s="42"/>
-      <c r="D8" s="18"/>
+    <row r="8" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>192</v>
+      </c>
       <c r="G8" s="14" t="s">
         <v>103</v>
       </c>
@@ -4681,9 +4722,14 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="41"/>
-      <c r="C9" s="41"/>
-      <c r="D9" s="18"/>
+      <c r="B9" s="40" t="s">
+        <v>86</v>
+      </c>
+      <c r="C9" s="40" t="s">
+        <v>87</v>
+      </c>
+      <c r="D9" s="49"/>
+      <c r="E9" s="49"/>
       <c r="G9" s="14" t="s">
         <v>88</v>
       </c>
@@ -4698,9 +4744,14 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="41"/>
-      <c r="C10" s="41"/>
-      <c r="D10" s="18"/>
+      <c r="B10" s="50" t="s">
+        <v>103</v>
+      </c>
+      <c r="C10" s="50" t="s">
+        <v>100</v>
+      </c>
+      <c r="D10" s="49"/>
+      <c r="E10" s="49"/>
       <c r="G10" s="14" t="s">
         <v>120</v>
       </c>
@@ -4715,9 +4766,12 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="42"/>
-      <c r="C11" s="42"/>
-      <c r="D11" s="18"/>
+      <c r="B11" s="49"/>
+      <c r="C11" s="50" t="s">
+        <v>92</v>
+      </c>
+      <c r="D11" s="49"/>
+      <c r="E11" s="49"/>
       <c r="G11" s="14" t="s">
         <v>125</v>
       </c>
@@ -4732,9 +4786,12 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="41"/>
-      <c r="C12" s="41"/>
-      <c r="D12" s="18"/>
+      <c r="B12" s="49"/>
+      <c r="C12" s="50" t="s">
+        <v>101</v>
+      </c>
+      <c r="D12" s="49"/>
+      <c r="E12" s="49"/>
       <c r="G12" s="14" t="s">
         <v>126</v>
       </c>
@@ -4749,9 +4806,12 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="41"/>
-      <c r="C13" s="41"/>
-      <c r="D13" s="18"/>
+      <c r="B13" s="49"/>
+      <c r="C13" s="50" t="s">
+        <v>85</v>
+      </c>
+      <c r="D13" s="49"/>
+      <c r="E13" s="49"/>
       <c r="G13" s="14" t="s">
         <v>127</v>
       </c>
@@ -4766,9 +4826,12 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="42"/>
-      <c r="C14" s="42"/>
-      <c r="D14" s="18"/>
+      <c r="B14" s="49"/>
+      <c r="C14" s="50" t="s">
+        <v>91</v>
+      </c>
+      <c r="D14" s="49"/>
+      <c r="E14" s="49"/>
       <c r="G14" s="14" t="s">
         <v>105</v>
       </c>
@@ -4783,9 +4846,10 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="41"/>
-      <c r="C15" s="41"/>
-      <c r="D15" s="18"/>
+      <c r="B15" s="49"/>
+      <c r="C15" s="49"/>
+      <c r="D15" s="49"/>
+      <c r="E15" s="49"/>
       <c r="G15" s="14" t="s">
         <v>96</v>
       </c>
@@ -4800,9 +4864,10 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="41"/>
-      <c r="C16" s="41"/>
-      <c r="D16" s="18"/>
+      <c r="B16" s="49"/>
+      <c r="C16" s="49"/>
+      <c r="D16" s="49"/>
+      <c r="E16" s="49"/>
       <c r="G16" s="19" t="s">
         <v>86</v>
       </c>
@@ -4816,7 +4881,11 @@
         <v>79</v>
       </c>
     </row>
-    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B17" s="49"/>
+      <c r="C17" s="49"/>
+      <c r="D17" s="49"/>
+      <c r="E17" s="49"/>
       <c r="G17" s="19" t="s">
         <v>135</v>
       </c>
@@ -4830,7 +4899,11 @@
         <v>79</v>
       </c>
     </row>
-    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="49"/>
+      <c r="C18" s="49"/>
+      <c r="D18" s="49"/>
+      <c r="E18" s="49"/>
       <c r="G18" s="20" t="s">
         <v>128</v>
       </c>
@@ -4844,7 +4917,11 @@
         <v>79</v>
       </c>
     </row>
-    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="49"/>
+      <c r="C19" s="49"/>
+      <c r="D19" s="49"/>
+      <c r="E19" s="49"/>
       <c r="G19" s="20" t="s">
         <v>119</v>
       </c>
@@ -4858,7 +4935,11 @@
         <v>79</v>
       </c>
     </row>
-    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="49"/>
+      <c r="C20" s="49"/>
+      <c r="D20" s="49"/>
+      <c r="E20" s="49"/>
       <c r="G20" s="34" t="s">
         <v>129</v>
       </c>
@@ -4872,7 +4953,11 @@
         <v>79</v>
       </c>
     </row>
-    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="49"/>
+      <c r="C21" s="49"/>
+      <c r="D21" s="49"/>
+      <c r="E21" s="49"/>
       <c r="K21" s="24" t="s">
         <v>92</v>
       </c>
@@ -4880,63 +4965,75 @@
         <v>79</v>
       </c>
     </row>
-    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B22" s="49"/>
+      <c r="C22" s="49"/>
+      <c r="D22" s="49"/>
+      <c r="E22" s="49"/>
       <c r="K22" s="31"/>
       <c r="L22" s="17"/>
     </row>
-    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B23" s="49"/>
+      <c r="C23" s="49"/>
+      <c r="D23" s="49"/>
+      <c r="E23" s="49"/>
       <c r="K23" s="22"/>
       <c r="L23" s="22"/>
     </row>
-    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B24" s="49"/>
+      <c r="C24" s="49"/>
+      <c r="D24" s="49"/>
+      <c r="E24" s="49"/>
       <c r="G24" s="22"/>
       <c r="H24" s="22"/>
       <c r="K24" s="22"/>
       <c r="L24" s="22"/>
     </row>
-    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G25" s="22"/>
       <c r="H25" s="22"/>
       <c r="K25" s="22"/>
       <c r="L25" s="22"/>
     </row>
-    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G26" s="22"/>
       <c r="H26" s="22"/>
       <c r="K26" s="22"/>
       <c r="L26" s="22"/>
     </row>
-    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G27" s="22"/>
       <c r="H27" s="22"/>
       <c r="K27" s="22"/>
       <c r="L27" s="22"/>
     </row>
-    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="22"/>
       <c r="H28" s="22"/>
       <c r="K28" s="22"/>
       <c r="L28" s="22"/>
     </row>
-    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G29" s="22"/>
       <c r="H29" s="22"/>
       <c r="K29" s="22"/>
       <c r="L29" s="22"/>
     </row>
-    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G30" s="22"/>
       <c r="H30" s="22"/>
       <c r="K30" s="22"/>
       <c r="L30" s="22"/>
     </row>
-    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G31" s="22"/>
       <c r="H31" s="22"/>
       <c r="K31" s="22"/>
       <c r="L31" s="22"/>
     </row>
-    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G32" s="22"/>
       <c r="H32" s="22"/>
       <c r="K32" s="22"/>
@@ -5014,17 +5111,18 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="43" t="s">
+      <c r="B2" s="42" t="s">
         <v>175</v>
       </c>
-      <c r="C2" s="44"/>
-      <c r="D2" s="45"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="44"/>
       <c r="G2" s="2" t="s">
         <v>76</v>
       </c>
@@ -5039,11 +5137,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="46" t="s">
+      <c r="B3" s="45" t="s">
         <v>181</v>
       </c>
-      <c r="C3" s="47"/>
-      <c r="D3" s="48"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="47"/>
       <c r="G3" s="25" t="s">
         <v>128</v>
       </c>
@@ -5120,7 +5218,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="41"/>
       <c r="C7" s="41"/>
       <c r="D7" s="18"/>
@@ -5137,10 +5235,19 @@
         <v>79</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="42"/>
-      <c r="C8" s="42"/>
-      <c r="D8" s="18"/>
+    <row r="8" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>192</v>
+      </c>
       <c r="G8" s="15" t="s">
         <v>127</v>
       </c>
@@ -5155,9 +5262,16 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="41"/>
-      <c r="C9" s="41"/>
-      <c r="D9" s="18"/>
+      <c r="B9" s="40" t="s">
+        <v>142</v>
+      </c>
+      <c r="C9" s="40" t="s">
+        <v>100</v>
+      </c>
+      <c r="D9" s="49"/>
+      <c r="E9" s="40" t="s">
+        <v>99</v>
+      </c>
       <c r="G9" s="15" t="s">
         <v>126</v>
       </c>
@@ -5172,9 +5286,16 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="41"/>
-      <c r="C10" s="41"/>
-      <c r="D10" s="18"/>
+      <c r="B10" s="50" t="s">
+        <v>141</v>
+      </c>
+      <c r="C10" s="50" t="s">
+        <v>92</v>
+      </c>
+      <c r="D10" s="49"/>
+      <c r="E10" s="50" t="s">
+        <v>95</v>
+      </c>
       <c r="G10" s="27" t="s">
         <v>105</v>
       </c>
@@ -5189,9 +5310,14 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="42"/>
-      <c r="C11" s="42"/>
-      <c r="D11" s="18"/>
+      <c r="B11" s="49"/>
+      <c r="C11" s="50" t="s">
+        <v>89</v>
+      </c>
+      <c r="D11" s="49"/>
+      <c r="E11" s="50" t="s">
+        <v>102</v>
+      </c>
       <c r="G11" s="27" t="s">
         <v>103</v>
       </c>
@@ -5206,9 +5332,12 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B12" s="41"/>
-      <c r="C12" s="41"/>
-      <c r="D12" s="18"/>
+      <c r="B12" s="49"/>
+      <c r="C12" s="50" t="s">
+        <v>84</v>
+      </c>
+      <c r="D12" s="49"/>
+      <c r="E12" s="49"/>
       <c r="G12" s="27" t="s">
         <v>136</v>
       </c>
@@ -5223,9 +5352,12 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B13" s="41"/>
-      <c r="C13" s="41"/>
-      <c r="D13" s="18"/>
+      <c r="B13" s="49"/>
+      <c r="C13" s="50" t="s">
+        <v>101</v>
+      </c>
+      <c r="D13" s="49"/>
+      <c r="E13" s="49"/>
       <c r="G13" s="14" t="s">
         <v>139</v>
       </c>
@@ -5240,9 +5372,12 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="42"/>
-      <c r="C14" s="42"/>
-      <c r="D14" s="18"/>
+      <c r="B14" s="49"/>
+      <c r="C14" s="50" t="s">
+        <v>94</v>
+      </c>
+      <c r="D14" s="49"/>
+      <c r="E14" s="49"/>
       <c r="G14" s="14" t="s">
         <v>93</v>
       </c>
@@ -5257,9 +5392,10 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="41"/>
-      <c r="C15" s="41"/>
-      <c r="D15" s="18"/>
+      <c r="B15" s="49"/>
+      <c r="C15" s="49"/>
+      <c r="D15" s="49"/>
+      <c r="E15" s="49"/>
       <c r="G15" s="28" t="s">
         <v>96</v>
       </c>
@@ -5274,9 +5410,10 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="41"/>
-      <c r="C16" s="41"/>
-      <c r="D16" s="18"/>
+      <c r="B16" s="49"/>
+      <c r="C16" s="49"/>
+      <c r="D16" s="49"/>
+      <c r="E16" s="49"/>
       <c r="G16" s="17"/>
       <c r="H16" s="17"/>
       <c r="K16" s="20" t="s">
@@ -5286,7 +5423,11 @@
         <v>79</v>
       </c>
     </row>
-    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B17" s="49"/>
+      <c r="C17" s="49"/>
+      <c r="D17" s="49"/>
+      <c r="E17" s="49"/>
       <c r="G17" s="22"/>
       <c r="H17" s="22"/>
       <c r="K17" s="20" t="s">
@@ -5296,7 +5437,11 @@
         <v>79</v>
       </c>
     </row>
-    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="49"/>
+      <c r="C18" s="49"/>
+      <c r="D18" s="49"/>
+      <c r="E18" s="49"/>
       <c r="G18" s="22"/>
       <c r="H18" s="22"/>
       <c r="K18" s="20" t="s">
@@ -5306,7 +5451,11 @@
         <v>79</v>
       </c>
     </row>
-    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="49"/>
+      <c r="C19" s="49"/>
+      <c r="D19" s="49"/>
+      <c r="E19" s="49"/>
       <c r="G19" s="22"/>
       <c r="H19" s="22"/>
       <c r="K19" s="20" t="s">
@@ -5316,7 +5465,11 @@
         <v>79</v>
       </c>
     </row>
-    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="49"/>
+      <c r="C20" s="49"/>
+      <c r="D20" s="49"/>
+      <c r="E20" s="49"/>
       <c r="G20" s="22"/>
       <c r="H20" s="22"/>
       <c r="K20" s="19" t="s">
@@ -5326,7 +5479,11 @@
         <v>79</v>
       </c>
     </row>
-    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="49"/>
+      <c r="C21" s="49"/>
+      <c r="D21" s="49"/>
+      <c r="E21" s="49"/>
       <c r="G21" s="22"/>
       <c r="H21" s="22"/>
       <c r="K21" s="19" t="s">
@@ -5336,7 +5493,11 @@
         <v>79</v>
       </c>
     </row>
-    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B22" s="49"/>
+      <c r="C22" s="49"/>
+      <c r="D22" s="49"/>
+      <c r="E22" s="49"/>
       <c r="G22" s="22"/>
       <c r="H22" s="22"/>
       <c r="K22" s="19" t="s">
@@ -5346,7 +5507,11 @@
         <v>79</v>
       </c>
     </row>
-    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B23" s="49"/>
+      <c r="C23" s="49"/>
+      <c r="D23" s="49"/>
+      <c r="E23" s="49"/>
       <c r="G23" s="22"/>
       <c r="H23" s="22"/>
       <c r="K23" s="14" t="s">
@@ -5356,7 +5521,11 @@
         <v>79</v>
       </c>
     </row>
-    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B24" s="49"/>
+      <c r="C24" s="49"/>
+      <c r="D24" s="49"/>
+      <c r="E24" s="49"/>
       <c r="G24" s="22"/>
       <c r="H24" s="22"/>
       <c r="K24" s="15" t="s">
@@ -5366,7 +5535,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G25" s="22"/>
       <c r="H25" s="22"/>
       <c r="K25" s="15" t="s">
@@ -5376,7 +5545,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G26" s="22"/>
       <c r="H26" s="22"/>
       <c r="K26" s="15" t="s">
@@ -5386,7 +5555,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G27" s="22"/>
       <c r="H27" s="22"/>
       <c r="K27" s="21" t="s">
@@ -5396,31 +5565,31 @@
         <v>79</v>
       </c>
     </row>
-    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="22"/>
       <c r="H28" s="22"/>
       <c r="K28" s="17"/>
       <c r="L28" s="17"/>
     </row>
-    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G29" s="22"/>
       <c r="H29" s="22"/>
       <c r="K29" s="22"/>
       <c r="L29" s="22"/>
     </row>
-    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G30" s="22"/>
       <c r="H30" s="22"/>
       <c r="K30" s="22"/>
       <c r="L30" s="22"/>
     </row>
-    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G31" s="22"/>
       <c r="H31" s="22"/>
       <c r="K31" s="22"/>
       <c r="L31" s="22"/>
     </row>
-    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G32" s="22"/>
       <c r="H32" s="22"/>
       <c r="K32" s="22"/>
@@ -5497,17 +5666,18 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="22.85546875" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="43" t="s">
+      <c r="B2" s="42" t="s">
         <v>175</v>
       </c>
-      <c r="C2" s="44"/>
-      <c r="D2" s="45"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="44"/>
       <c r="G2" s="2" t="s">
         <v>76</v>
       </c>
@@ -5522,11 +5692,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="46" t="s">
+      <c r="B3" s="45" t="s">
         <v>176</v>
       </c>
-      <c r="C3" s="47"/>
-      <c r="D3" s="48"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="47"/>
       <c r="G3" s="13" t="s">
         <v>78</v>
       </c>
@@ -5603,7 +5773,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="41"/>
       <c r="C7" s="41"/>
       <c r="D7" s="18"/>
@@ -5620,10 +5790,19 @@
         <v>79</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="42"/>
-      <c r="C8" s="42"/>
-      <c r="D8" s="18"/>
+    <row r="8" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>192</v>
+      </c>
       <c r="G8" s="27" t="s">
         <v>120</v>
       </c>
@@ -5638,9 +5817,14 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="41"/>
-      <c r="C9" s="41"/>
-      <c r="D9" s="18"/>
+      <c r="B9" s="40" t="s">
+        <v>86</v>
+      </c>
+      <c r="C9" s="40" t="s">
+        <v>87</v>
+      </c>
+      <c r="D9" s="49"/>
+      <c r="E9" s="49"/>
       <c r="G9" s="27" t="s">
         <v>127</v>
       </c>
@@ -5655,9 +5839,14 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="41"/>
-      <c r="C10" s="41"/>
-      <c r="D10" s="18"/>
+      <c r="B10" s="50" t="s">
+        <v>193</v>
+      </c>
+      <c r="C10" s="50" t="s">
+        <v>100</v>
+      </c>
+      <c r="D10" s="49"/>
+      <c r="E10" s="49"/>
       <c r="G10" s="27" t="s">
         <v>105</v>
       </c>
@@ -5672,9 +5861,14 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="42"/>
-      <c r="C11" s="42"/>
-      <c r="D11" s="18"/>
+      <c r="B11" s="50" t="s">
+        <v>141</v>
+      </c>
+      <c r="C11" s="50" t="s">
+        <v>101</v>
+      </c>
+      <c r="D11" s="49"/>
+      <c r="E11" s="49"/>
       <c r="G11" s="27" t="s">
         <v>96</v>
       </c>
@@ -5689,9 +5883,14 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="41"/>
-      <c r="C12" s="41"/>
-      <c r="D12" s="18"/>
+      <c r="B12" s="50" t="s">
+        <v>142</v>
+      </c>
+      <c r="C12" s="50" t="s">
+        <v>102</v>
+      </c>
+      <c r="D12" s="49"/>
+      <c r="E12" s="49"/>
       <c r="G12" s="14" t="s">
         <v>136</v>
       </c>
@@ -5706,9 +5905,12 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="41"/>
-      <c r="C13" s="41"/>
-      <c r="D13" s="18"/>
+      <c r="B13" s="49"/>
+      <c r="C13" s="50" t="s">
+        <v>85</v>
+      </c>
+      <c r="D13" s="49"/>
+      <c r="E13" s="49"/>
       <c r="G13" s="14" t="s">
         <v>126</v>
       </c>
@@ -5723,9 +5925,10 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="42"/>
-      <c r="C14" s="42"/>
-      <c r="D14" s="18"/>
+      <c r="B14" s="49"/>
+      <c r="C14" s="49"/>
+      <c r="D14" s="49"/>
+      <c r="E14" s="49"/>
       <c r="G14" s="14" t="s">
         <v>119</v>
       </c>
@@ -5740,9 +5943,10 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="41"/>
-      <c r="C15" s="41"/>
-      <c r="D15" s="18"/>
+      <c r="B15" s="49"/>
+      <c r="C15" s="49"/>
+      <c r="D15" s="49"/>
+      <c r="E15" s="49"/>
       <c r="G15" s="14" t="s">
         <v>138</v>
       </c>
@@ -5757,9 +5961,10 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="41"/>
-      <c r="C16" s="41"/>
-      <c r="D16" s="18"/>
+      <c r="B16" s="49"/>
+      <c r="C16" s="49"/>
+      <c r="D16" s="49"/>
+      <c r="E16" s="49"/>
       <c r="G16" s="35" t="s">
         <v>115</v>
       </c>
@@ -5773,7 +5978,11 @@
         <v>79</v>
       </c>
     </row>
-    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B17" s="49"/>
+      <c r="C17" s="49"/>
+      <c r="D17" s="49"/>
+      <c r="E17" s="49"/>
       <c r="G17" s="35" t="s">
         <v>153</v>
       </c>
@@ -5787,7 +5996,11 @@
         <v>79</v>
       </c>
     </row>
-    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="49"/>
+      <c r="C18" s="49"/>
+      <c r="D18" s="49"/>
+      <c r="E18" s="49"/>
       <c r="G18" s="35" t="s">
         <v>154</v>
       </c>
@@ -5801,7 +6014,11 @@
         <v>79</v>
       </c>
     </row>
-    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="49"/>
+      <c r="C19" s="49"/>
+      <c r="D19" s="49"/>
+      <c r="E19" s="49"/>
       <c r="G19" s="36" t="s">
         <v>141</v>
       </c>
@@ -5815,7 +6032,11 @@
         <v>79</v>
       </c>
     </row>
-    <row r="20" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B20" s="49"/>
+      <c r="C20" s="49"/>
+      <c r="D20" s="49"/>
+      <c r="E20" s="49"/>
       <c r="G20" s="19" t="s">
         <v>121</v>
       </c>
@@ -5829,7 +6050,11 @@
         <v>79</v>
       </c>
     </row>
-    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="49"/>
+      <c r="C21" s="49"/>
+      <c r="D21" s="49"/>
+      <c r="E21" s="49"/>
       <c r="G21" s="19" t="s">
         <v>142</v>
       </c>
@@ -5843,7 +6068,11 @@
         <v>79</v>
       </c>
     </row>
-    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B22" s="49"/>
+      <c r="C22" s="49"/>
+      <c r="D22" s="49"/>
+      <c r="E22" s="49"/>
       <c r="G22" s="20" t="s">
         <v>122</v>
       </c>
@@ -5857,7 +6086,11 @@
         <v>79</v>
       </c>
     </row>
-    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B23" s="49"/>
+      <c r="C23" s="49"/>
+      <c r="D23" s="49"/>
+      <c r="E23" s="49"/>
       <c r="G23" s="20" t="s">
         <v>143</v>
       </c>
@@ -5871,7 +6104,11 @@
         <v>79</v>
       </c>
     </row>
-    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B24" s="49"/>
+      <c r="C24" s="49"/>
+      <c r="D24" s="49"/>
+      <c r="E24" s="49"/>
       <c r="G24" s="20" t="s">
         <v>144</v>
       </c>
@@ -5885,7 +6122,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G25" s="20" t="s">
         <v>145</v>
       </c>
@@ -5899,7 +6136,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G26" s="20" t="s">
         <v>98</v>
       </c>
@@ -5913,7 +6150,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G27" s="34" t="s">
         <v>146</v>
       </c>
@@ -5927,7 +6164,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="34" t="s">
         <v>147</v>
       </c>
@@ -5941,7 +6178,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G29" s="15" t="s">
         <v>148</v>
       </c>
@@ -5955,7 +6192,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G30" s="15" t="s">
         <v>149</v>
       </c>
@@ -5969,7 +6206,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G31" s="34" t="s">
         <v>150</v>
       </c>
@@ -5983,7 +6220,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G32" s="15" t="s">
         <v>109</v>
       </c>
@@ -6080,17 +6317,18 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="43" t="s">
+      <c r="B2" s="42" t="s">
         <v>175</v>
       </c>
-      <c r="C2" s="44"/>
-      <c r="D2" s="45"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="44"/>
       <c r="G2" s="2" t="s">
         <v>76</v>
       </c>
@@ -6105,11 +6343,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="46" t="s">
+      <c r="B3" s="45" t="s">
         <v>187</v>
       </c>
-      <c r="C3" s="47"/>
-      <c r="D3" s="48"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="47"/>
       <c r="G3" s="13" t="s">
         <v>78</v>
       </c>
@@ -6186,7 +6424,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="41"/>
       <c r="C7" s="41"/>
       <c r="D7" s="18"/>
@@ -6203,10 +6441,19 @@
         <v>79</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="42"/>
-      <c r="C8" s="42"/>
-      <c r="D8" s="18"/>
+    <row r="8" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>192</v>
+      </c>
       <c r="G8" s="20" t="s">
         <v>126</v>
       </c>
@@ -6221,9 +6468,14 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="41"/>
-      <c r="C9" s="41"/>
-      <c r="D9" s="18"/>
+      <c r="B9" s="40" t="s">
+        <v>86</v>
+      </c>
+      <c r="C9" s="49"/>
+      <c r="D9" s="49"/>
+      <c r="E9" s="40" t="s">
+        <v>100</v>
+      </c>
       <c r="G9" s="20" t="s">
         <v>88</v>
       </c>
@@ -6238,9 +6490,14 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="41"/>
-      <c r="C10" s="41"/>
-      <c r="D10" s="18"/>
+      <c r="B10" s="50" t="s">
+        <v>144</v>
+      </c>
+      <c r="C10" s="49"/>
+      <c r="D10" s="49"/>
+      <c r="E10" s="50" t="s">
+        <v>92</v>
+      </c>
       <c r="G10" s="20" t="s">
         <v>119</v>
       </c>
@@ -6255,9 +6512,14 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="42"/>
-      <c r="C11" s="42"/>
-      <c r="D11" s="18"/>
+      <c r="B11" s="50" t="s">
+        <v>143</v>
+      </c>
+      <c r="C11" s="49"/>
+      <c r="D11" s="49"/>
+      <c r="E11" s="50" t="s">
+        <v>89</v>
+      </c>
       <c r="G11" s="20" t="s">
         <v>127</v>
       </c>
@@ -6272,9 +6534,14 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="41"/>
-      <c r="C12" s="41"/>
-      <c r="D12" s="18"/>
+      <c r="B12" s="50" t="s">
+        <v>103</v>
+      </c>
+      <c r="C12" s="49"/>
+      <c r="D12" s="49"/>
+      <c r="E12" s="50" t="s">
+        <v>84</v>
+      </c>
       <c r="G12" s="20" t="s">
         <v>103</v>
       </c>
@@ -6289,9 +6556,10 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="41"/>
-      <c r="C13" s="41"/>
-      <c r="D13" s="18"/>
+      <c r="B13" s="49"/>
+      <c r="C13" s="49"/>
+      <c r="D13" s="49"/>
+      <c r="E13" s="49"/>
       <c r="G13" s="20" t="s">
         <v>125</v>
       </c>
@@ -6306,9 +6574,10 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="42"/>
-      <c r="C14" s="42"/>
-      <c r="D14" s="18"/>
+      <c r="B14" s="49"/>
+      <c r="C14" s="49"/>
+      <c r="D14" s="49"/>
+      <c r="E14" s="49"/>
       <c r="G14" s="20" t="s">
         <v>145</v>
       </c>
@@ -6323,9 +6592,10 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="41"/>
-      <c r="C15" s="41"/>
-      <c r="D15" s="18"/>
+      <c r="B15" s="49"/>
+      <c r="C15" s="49"/>
+      <c r="D15" s="49"/>
+      <c r="E15" s="49"/>
       <c r="G15" s="14" t="s">
         <v>161</v>
       </c>
@@ -6340,9 +6610,10 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="41"/>
-      <c r="C16" s="41"/>
-      <c r="D16" s="18"/>
+      <c r="B16" s="49"/>
+      <c r="C16" s="49"/>
+      <c r="D16" s="49"/>
+      <c r="E16" s="49"/>
       <c r="G16" s="14" t="s">
         <v>138</v>
       </c>
@@ -6356,7 +6627,11 @@
         <v>79</v>
       </c>
     </row>
-    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B17" s="49"/>
+      <c r="C17" s="49"/>
+      <c r="D17" s="49"/>
+      <c r="E17" s="49"/>
       <c r="G17" s="14" t="s">
         <v>98</v>
       </c>
@@ -6370,7 +6645,11 @@
         <v>79</v>
       </c>
     </row>
-    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="49"/>
+      <c r="C18" s="49"/>
+      <c r="D18" s="49"/>
+      <c r="E18" s="49"/>
       <c r="G18" s="27" t="s">
         <v>86</v>
       </c>
@@ -6384,7 +6663,11 @@
         <v>79</v>
       </c>
     </row>
-    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="49"/>
+      <c r="C19" s="49"/>
+      <c r="D19" s="49"/>
+      <c r="E19" s="49"/>
       <c r="G19" s="27" t="s">
         <v>120</v>
       </c>
@@ -6398,7 +6681,11 @@
         <v>79</v>
       </c>
     </row>
-    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="49"/>
+      <c r="C20" s="49"/>
+      <c r="D20" s="49"/>
+      <c r="E20" s="49"/>
       <c r="G20" s="27" t="s">
         <v>143</v>
       </c>
@@ -6412,7 +6699,11 @@
         <v>79</v>
       </c>
     </row>
-    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="49"/>
+      <c r="C21" s="49"/>
+      <c r="D21" s="49"/>
+      <c r="E21" s="49"/>
       <c r="G21" s="27" t="s">
         <v>144</v>
       </c>
@@ -6426,7 +6717,11 @@
         <v>79</v>
       </c>
     </row>
-    <row r="22" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B22" s="49"/>
+      <c r="C22" s="49"/>
+      <c r="D22" s="49"/>
+      <c r="E22" s="49"/>
       <c r="G22" s="27" t="s">
         <v>121</v>
       </c>
@@ -6440,7 +6735,11 @@
         <v>79</v>
       </c>
     </row>
-    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B23" s="49"/>
+      <c r="C23" s="49"/>
+      <c r="D23" s="49"/>
+      <c r="E23" s="49"/>
       <c r="G23" s="27" t="s">
         <v>122</v>
       </c>
@@ -6454,7 +6753,11 @@
         <v>79</v>
       </c>
     </row>
-    <row r="24" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B24" s="49"/>
+      <c r="C24" s="49"/>
+      <c r="D24" s="49"/>
+      <c r="E24" s="49"/>
       <c r="G24" s="27" t="s">
         <v>109</v>
       </c>
@@ -6468,7 +6771,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G25" s="37" t="s">
         <v>162</v>
       </c>
@@ -6482,7 +6785,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G26" s="17"/>
       <c r="H26" s="17"/>
       <c r="K26" s="15" t="s">
@@ -6492,7 +6795,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G27" s="22"/>
       <c r="H27" s="22"/>
       <c r="K27" s="21" t="s">
@@ -6502,31 +6805,31 @@
         <v>79</v>
       </c>
     </row>
-    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="22"/>
       <c r="H28" s="22"/>
       <c r="K28" s="17"/>
       <c r="L28" s="17"/>
     </row>
-    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G29" s="22"/>
       <c r="H29" s="22"/>
       <c r="K29" s="22"/>
       <c r="L29" s="22"/>
     </row>
-    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G30" s="22"/>
       <c r="H30" s="22"/>
       <c r="K30" s="22"/>
       <c r="L30" s="22"/>
     </row>
-    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G31" s="22"/>
       <c r="H31" s="22"/>
       <c r="K31" s="22"/>
       <c r="L31" s="22"/>
     </row>
-    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G32" s="22"/>
       <c r="H32" s="22"/>
       <c r="K32" s="22"/>
@@ -6603,17 +6906,18 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="23" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="43" t="s">
+      <c r="B2" s="42" t="s">
         <v>175</v>
       </c>
-      <c r="C2" s="44"/>
-      <c r="D2" s="45"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="44"/>
       <c r="G2" s="2" t="s">
         <v>76</v>
       </c>
@@ -6628,11 +6932,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="46" t="s">
+      <c r="B3" s="45" t="s">
         <v>187</v>
       </c>
-      <c r="C3" s="47"/>
-      <c r="D3" s="48"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="47"/>
       <c r="G3" s="13" t="s">
         <v>78</v>
       </c>
@@ -6709,7 +7013,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="41"/>
       <c r="C7" s="41"/>
       <c r="D7" s="18"/>
@@ -6726,10 +7030,19 @@
         <v>117</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B8" s="42"/>
-      <c r="C8" s="42"/>
-      <c r="D8" s="18"/>
+    <row r="8" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>192</v>
+      </c>
       <c r="G8" s="15" t="s">
         <v>103</v>
       </c>
@@ -6744,9 +7057,16 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B9" s="41"/>
-      <c r="C9" s="41"/>
-      <c r="D9" s="18"/>
+      <c r="B9" s="40" t="s">
+        <v>86</v>
+      </c>
+      <c r="C9" s="49"/>
+      <c r="D9" s="40" t="s">
+        <v>146</v>
+      </c>
+      <c r="E9" s="48" t="s">
+        <v>94</v>
+      </c>
       <c r="G9" s="15" t="s">
         <v>88</v>
       </c>
@@ -6761,9 +7081,14 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B10" s="41"/>
-      <c r="C10" s="41"/>
-      <c r="D10" s="18"/>
+      <c r="B10" s="40" t="s">
+        <v>122</v>
+      </c>
+      <c r="C10" s="49"/>
+      <c r="D10" s="49"/>
+      <c r="E10" s="40" t="s">
+        <v>91</v>
+      </c>
       <c r="G10" s="34" t="s">
         <v>118</v>
       </c>
@@ -6778,9 +7103,12 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B11" s="42"/>
-      <c r="C11" s="42"/>
-      <c r="D11" s="18"/>
+      <c r="B11" s="40" t="s">
+        <v>142</v>
+      </c>
+      <c r="C11" s="49"/>
+      <c r="D11" s="49"/>
+      <c r="E11" s="49"/>
       <c r="G11" s="34" t="s">
         <v>166</v>
       </c>
@@ -6795,9 +7123,12 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B12" s="41"/>
-      <c r="C12" s="41"/>
-      <c r="D12" s="18"/>
+      <c r="B12" s="40" t="s">
+        <v>166</v>
+      </c>
+      <c r="C12" s="49"/>
+      <c r="D12" s="49"/>
+      <c r="E12" s="49"/>
       <c r="G12" s="15" t="s">
         <v>98</v>
       </c>
@@ -6812,9 +7143,10 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B13" s="41"/>
-      <c r="C13" s="41"/>
-      <c r="D13" s="18"/>
+      <c r="B13" s="49"/>
+      <c r="C13" s="49"/>
+      <c r="D13" s="49"/>
+      <c r="E13" s="49"/>
       <c r="G13" s="34" t="s">
         <v>116</v>
       </c>
@@ -6829,9 +7161,10 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B14" s="42"/>
-      <c r="C14" s="42"/>
-      <c r="D14" s="18"/>
+      <c r="B14" s="49"/>
+      <c r="C14" s="49"/>
+      <c r="D14" s="49"/>
+      <c r="E14" s="49"/>
       <c r="G14" s="19" t="s">
         <v>127</v>
       </c>
@@ -6846,9 +7179,10 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B15" s="41"/>
-      <c r="C15" s="41"/>
-      <c r="D15" s="18"/>
+      <c r="B15" s="49"/>
+      <c r="C15" s="49"/>
+      <c r="D15" s="49"/>
+      <c r="E15" s="49"/>
       <c r="G15" s="19" t="s">
         <v>135</v>
       </c>
@@ -6863,9 +7197,10 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B16" s="41"/>
-      <c r="C16" s="41"/>
-      <c r="D16" s="18"/>
+      <c r="B16" s="49"/>
+      <c r="C16" s="49"/>
+      <c r="D16" s="49"/>
+      <c r="E16" s="49"/>
       <c r="G16" s="19" t="s">
         <v>93</v>
       </c>
@@ -6879,7 +7214,11 @@
         <v>117</v>
       </c>
     </row>
-    <row r="17" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B17" s="49"/>
+      <c r="C17" s="49"/>
+      <c r="D17" s="49"/>
+      <c r="E17" s="49"/>
       <c r="G17" s="36" t="s">
         <v>167</v>
       </c>
@@ -6893,7 +7232,11 @@
         <v>117</v>
       </c>
     </row>
-    <row r="18" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B18" s="49"/>
+      <c r="C18" s="49"/>
+      <c r="D18" s="49"/>
+      <c r="E18" s="49"/>
       <c r="G18" s="36" t="s">
         <v>161</v>
       </c>
@@ -6907,7 +7250,11 @@
         <v>117</v>
       </c>
     </row>
-    <row r="19" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B19" s="49"/>
+      <c r="C19" s="49"/>
+      <c r="D19" s="49"/>
+      <c r="E19" s="49"/>
       <c r="G19" s="36" t="s">
         <v>168</v>
       </c>
@@ -6921,7 +7268,11 @@
         <v>117</v>
       </c>
     </row>
-    <row r="20" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B20" s="49"/>
+      <c r="C20" s="49"/>
+      <c r="D20" s="49"/>
+      <c r="E20" s="49"/>
       <c r="G20" s="19" t="s">
         <v>109</v>
       </c>
@@ -6935,7 +7286,11 @@
         <v>117</v>
       </c>
     </row>
-    <row r="21" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B21" s="49"/>
+      <c r="C21" s="49"/>
+      <c r="D21" s="49"/>
+      <c r="E21" s="49"/>
       <c r="G21" s="27" t="s">
         <v>144</v>
       </c>
@@ -6949,7 +7304,11 @@
         <v>117</v>
       </c>
     </row>
-    <row r="22" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B22" s="49"/>
+      <c r="C22" s="49"/>
+      <c r="D22" s="49"/>
+      <c r="E22" s="49"/>
       <c r="G22" s="27" t="s">
         <v>105</v>
       </c>
@@ -6963,7 +7322,11 @@
         <v>117</v>
       </c>
     </row>
-    <row r="23" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B23" s="49"/>
+      <c r="C23" s="49"/>
+      <c r="D23" s="49"/>
+      <c r="E23" s="49"/>
       <c r="G23" s="14" t="s">
         <v>120</v>
       </c>
@@ -6977,7 +7340,11 @@
         <v>117</v>
       </c>
     </row>
-    <row r="24" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B24" s="49"/>
+      <c r="C24" s="49"/>
+      <c r="D24" s="49"/>
+      <c r="E24" s="49"/>
       <c r="G24" s="14" t="s">
         <v>125</v>
       </c>
@@ -6991,7 +7358,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="25" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G25" s="14" t="s">
         <v>126</v>
       </c>
@@ -7005,7 +7372,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="26" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G26" s="14" t="s">
         <v>148</v>
       </c>
@@ -7019,7 +7386,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="27" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G27" s="14" t="s">
         <v>149</v>
       </c>
@@ -7033,7 +7400,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="28" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G28" s="14" t="s">
         <v>169</v>
       </c>
@@ -7047,7 +7414,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="29" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G29" s="14" t="s">
         <v>170</v>
       </c>
@@ -7061,7 +7428,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="30" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G30" s="20" t="s">
         <v>142</v>
       </c>
@@ -7071,7 +7438,7 @@
       <c r="K30" s="17"/>
       <c r="L30" s="17"/>
     </row>
-    <row r="31" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G31" s="20" t="s">
         <v>143</v>
       </c>
@@ -7081,7 +7448,7 @@
       <c r="K31" s="22"/>
       <c r="L31" s="22"/>
     </row>
-    <row r="32" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G32" s="38" t="s">
         <v>171</v>
       </c>
